--- a/ontology/contingency-data/京东三期/项目管理/风险/输出结果/风险信息.xlsx
+++ b/ontology/contingency-data/京东三期/项目管理/风险/输出结果/风险信息.xlsx
@@ -2934,7 +2934,7 @@
       </c>
       <c r="W21" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="W22" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="W23" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       </c>
       <c r="W24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-13 18:01:58</t>
+          <t>2026-06-13 18:18:23</t>
         </is>
       </c>
     </row>
